--- a/wk3/Conditional_Formatting_Tutorial.xlsx
+++ b/wk3/Conditional_Formatting_Tutorial.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jatin/Desktop/Learnings/Upright/Student_Repo/wk3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDB0AF8B-0222-764D-BB5D-59F281D93B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{322B127C-2EFF-F44A-8415-97BFCD344AC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="-4180" windowWidth="38400" windowHeight="18740" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="-4580" windowWidth="38400" windowHeight="21000" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Thresholds" sheetId="1" r:id="rId1"/>
@@ -280,107 +280,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1262,10 +1162,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D26">
-    <cfRule type="cellIs" dxfId="12" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
       <formula>3000</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
       <formula>5000</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1824,6 +1724,9 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:B26">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
